--- a/output/script.xlsx
+++ b/output/script.xlsx
@@ -1,37 +1,96 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DRuiDS\Coding\Project\content_creator\VideoAutomation\output\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADED83D-001D-4ED9-9F62-953F9D249636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>scene_1</t>
+  </si>
+  <si>
+    <t>scene_2</t>
+  </si>
+  <si>
+    <t>scene_3</t>
+  </si>
+  <si>
+    <t>scene_4</t>
+  </si>
+  <si>
+    <t>scene_5</t>
+  </si>
+  <si>
+    <t>scene_6</t>
+  </si>
+  <si>
+    <t>scene_7</t>
+  </si>
+  <si>
+    <t>scene_8</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:00-0:05', 'visual': ['Tampilan layar HP memperlihatkan logo Google dengan kotak pencarian.', "Animasi jari mengetik 'search engine pertama' di kotak pencarian."], 'narasi': 'Google memang raja search engine sekarang, tapi tahu gak ada mesin pencari sebelum Google?', 'prompt text to image': ["Close-up of a smartphone screen displaying the Google logo and search bar. The search bar has the words 'search engine pertama' being typed in.", 'Animated finger typing on a virtual keyboard on the phone screen. The style should be modern and clean.'], 'text in screen': 'Sebelum Google...'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:05-0:10', 'visual': ['Foto jadul komputer mainframe besar dengan banyak tape drive.', 'Tampilan interface command-line berwarna hijau pada layar hitam.'], 'narasi': 'Kenalan sama Arch! Ini search engine pertama di internet tahun 1990. Bentuknya kayak gini, rumit banget!', 'prompt text to image': ['A vintage photograph of a large mainframe computer with numerous tape drives and blinking lights. Focus on the scale and complexity of the machine.', 'A close-up of a command-line interface on a black screen with green text. The interface should show directory listings and file names.'], 'text in screen': 'Kenalan sama ARCH'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:10-0:15', 'visual': ['Animasi sederhana yang menunjukkan cara kerja Arch: user mengetik perintah, server mencari file, hasil ditampilkan dalam teks.'], 'narasi': 'Cara kerjanya? Kita ketik perintah, server cari file berdasarkan nama persis, lalu hasilnya... daftar file!', 'prompt text to image': ['A simplified animation illustrating how Arch works: a user types a command on a terminal, a server searches for files based on exact name, and the results are displayed as text.', 'The animation should be clean, minimalist, and easy to understand.'], 'text in screen': 'Cara Kerjanya?'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:15-0:20', 'visual': ['Animasi perbandingan: Arch dengan antarmuka teks vs. Google dengan antarmuka grafis dan gambar.'], 'narasi': 'Bandingkan sama Google sekarang... Jauh banget ya! Dulu nyari informasi sesusah ini!', 'prompt text to image': ["A split-screen animation comparing Arch's text-based interface with Google's modern graphical interface and images. Highlight the stark differences in user experience.", 'The style should clearly showcase the evolution from old to new.'], 'text in screen': 'Dulu vs Sekarang'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:20-0:25', 'visual': ['Ilustrasi orang frustrasi menggunakan Arch, lalu beralih menggunakan Google dan tersenyum.'], 'narasi': 'Pantesan Arch gak populer. Harus tahu nama file persis! Google lebih canggih, bisa cari pakai kata kunci.', 'prompt text to image': ["An illustration of a person looking frustrated while using Arch's command-line interface, then transitioning to using Google and smiling.", 'The illustration style should be cartoonish and expressive, conveying the difference in user satisfaction.'], 'text in screen': 'Kenapa Arch gak populer?'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:25-0:30', 'visual': ['Grafik yang menunjukkan pertumbuhan Google dan penurunan popularitas Arch.', "Teks 'Thank You, Google!'"], 'narasi': 'Jadi, Google datang mengubah segalanya! Terima kasih Google!', 'prompt text to image': ["A simple graph showing the growth of Google's popularity and the decline of Arch over time. The graph should be clean and easy to understand.", "Text overlay saying 'Thank You, Google!' in a playful font."], 'text in screen': 'Thank You, Google!'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:30-0:33', 'visual': ['Cuplikan layar ponsel menampilkan kolom komentar YouTube Shorts.', "Animasi tangan mengarah ke tombol 'Like' dan 'Subscribe'."], 'narasi': 'Gimana? Seru kan sejarah internet? Jangan lupa like dan subscribe ya!', 'prompt text to image': ['A screenshot of a mobile phone displaying the YouTube Shorts comment section.', "Animated hand pointing to the 'Like' and 'Subscribe' buttons."], 'text in screen': 'Like &amp; Subscribe!'}</t>
+  </si>
+  <si>
+    <t>{'durasi': '0:33-0:35', 'visual': ["Layar hitam dengan teks 'Follow for more tech history!'", 'Logo YouTube channel.'], 'narasi': 'Follow terus untuk sejarah teknologi lainnya!', 'prompt text to image': ["A black screen with the text 'Follow for more tech history!' in a bold, modern font.", 'The YouTube channel logo in the corner.'], 'text in screen': 'Follow for more!'}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +105,46 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,166 +432,77 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="8" width="26.140625" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>scene_1</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>scene_2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>scene_3</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scene_4</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>scene_5</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scene_6</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scene_7</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scene_8</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:00-0:05', 'visual': ['Tampilan layar HP memperlihatkan logo Google dengan kotak pencarian.', "Animasi jari mengetik 'search engine pertama' di kotak pencarian."], 'narasi': 'Google memang raja search engine sekarang, tapi tahu gak ada mesin pencari sebelum Google?', 'prompt text to image': ["Close-up of a smartphone screen displaying the Google logo and search bar. The search bar has the words 'search engine pertama' being typed in.", 'Animated finger typing on a virtual keyboard on the phone screen. The style should be modern and clean.'], 'text in screen': 'Sebelum Google...'}</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:05-0:10', 'visual': ['Foto jadul komputer mainframe besar dengan banyak tape drive.', 'Tampilan interface command-line berwarna hijau pada layar hitam.'], 'narasi': 'Kenalan sama Arch! Ini search engine pertama di internet tahun 1990. Bentuknya kayak gini, rumit banget!', 'prompt text to image': ['A vintage photograph of a large mainframe computer with numerous tape drives and blinking lights. Focus on the scale and complexity of the machine.', 'A close-up of a command-line interface on a black screen with green text. The interface should show directory listings and file names.'], 'text in screen': 'Kenalan sama ARCH'}</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:10-0:15', 'visual': ['Animasi sederhana yang menunjukkan cara kerja Arch: user mengetik perintah, server mencari file, hasil ditampilkan dalam teks.'], 'narasi': 'Cara kerjanya? Kita ketik perintah, server cari file berdasarkan nama persis, lalu hasilnya... daftar file!', 'prompt text to image': ['A simplified animation illustrating how Arch works: a user types a command on a terminal, a server searches for files based on exact name, and the results are displayed as text.', 'The animation should be clean, minimalist, and easy to understand.'], 'text in screen': 'Cara Kerjanya?'}</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:15-0:20', 'visual': ['Animasi perbandingan: Arch dengan antarmuka teks vs. Google dengan antarmuka grafis dan gambar.'], 'narasi': 'Bandingkan sama Google sekarang... Jauh banget ya! Dulu nyari informasi sesusah ini!', 'prompt text to image': ["A split-screen animation comparing Arch's text-based interface with Google's modern graphical interface and images. Highlight the stark differences in user experience.", 'The style should clearly showcase the evolution from old to new.'], 'text in screen': 'Dulu vs Sekarang'}</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:20-0:25', 'visual': ['Ilustrasi orang frustrasi menggunakan Arch, lalu beralih menggunakan Google dan tersenyum.'], 'narasi': 'Pantesan Arch gak populer. Harus tahu nama file persis! Google lebih canggih, bisa cari pakai kata kunci.', 'prompt text to image': ["An illustration of a person looking frustrated while using Arch's command-line interface, then transitioning to using Google and smiling.", 'The illustration style should be cartoonish and expressive, conveying the difference in user satisfaction.'], 'text in screen': 'Kenapa Arch gak populer?'}</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:25-0:30', 'visual': ['Grafik yang menunjukkan pertumbuhan Google dan penurunan popularitas Arch.', "Teks 'Thank You, Google!'"], 'narasi': 'Jadi, Google datang mengubah segalanya! Terima kasih Google!', 'prompt text to image': ["A simple graph showing the growth of Google's popularity and the decline of Arch over time. The graph should be clean and easy to understand.", "Text overlay saying 'Thank You, Google!' in a playful font."], 'text in screen': 'Thank You, Google!'}</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:30-0:33', 'visual': ['Cuplikan layar ponsel menampilkan kolom komentar YouTube Shorts.', "Animasi tangan mengarah ke tombol 'Like' dan 'Subscribe'."], 'narasi': 'Gimana? Seru kan sejarah internet? Jangan lupa like dan subscribe ya!', 'prompt text to image': ['A screenshot of a mobile phone displaying the YouTube Shorts comment section.', "Animated hand pointing to the 'Like' and 'Subscribe' buttons."], 'text in screen': 'Like &amp; Subscribe!'}</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>{'durasi': '0:33-0:35', 'visual': ["Layar hitam dengan teks 'Follow for more tech history!'", 'Logo YouTube channel.'], 'narasi': 'Follow terus untuk sejarah teknologi lainnya!', 'prompt text to image': ["A black screen with the text 'Follow for more tech history!' in a bold, modern font.", 'The YouTube channel logo in the corner.'], 'text in screen': 'Follow for more!'}</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="375" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="390" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="345" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="330" x14ac:dyDescent="0.25">
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="330" x14ac:dyDescent="0.25">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="285" x14ac:dyDescent="0.25">
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="285" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="H9" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
